--- a/Team-Data/2012-13/3-29-2012-13.xlsx
+++ b/Team-Data/2012-13/3-29-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E2" t="n">
         <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>0.548</v>
+        <v>0.556</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
@@ -679,7 +746,7 @@
         <v>37.6</v>
       </c>
       <c r="J2" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="K2" t="n">
         <v>0.465</v>
@@ -688,19 +755,19 @@
         <v>8.9</v>
       </c>
       <c r="M2" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0.38</v>
+        <v>0.379</v>
       </c>
       <c r="O2" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="P2" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.711</v>
+        <v>0.709</v>
       </c>
       <c r="R2" t="n">
         <v>9.199999999999999</v>
@@ -724,28 +791,28 @@
         <v>4.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.8</v>
+        <v>97.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -766,7 +833,7 @@
         <v>3</v>
       </c>
       <c r="AM2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN2" t="n">
         <v>4</v>
@@ -775,7 +842,7 @@
         <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ2" t="n">
         <v>26</v>
@@ -793,19 +860,19 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY2" t="n">
         <v>7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA2" t="n">
         <v>26</v>
@@ -814,7 +881,7 @@
         <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -843,37 +910,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="n">
         <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>0.528</v>
+        <v>0.521</v>
       </c>
       <c r="H3" t="n">
         <v>49.1</v>
       </c>
       <c r="I3" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J3" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L3" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.358</v>
+        <v>0.356</v>
       </c>
       <c r="O3" t="n">
         <v>16.6</v>
@@ -882,13 +949,13 @@
         <v>21.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R3" t="n">
         <v>8.1</v>
       </c>
       <c r="S3" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T3" t="n">
         <v>39.6</v>
@@ -903,25 +970,25 @@
         <v>8.4</v>
       </c>
       <c r="X3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y3" t="n">
         <v>4.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>96.2</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
         <v>14</v>
@@ -942,16 +1009,16 @@
         <v>27</v>
       </c>
       <c r="AK3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM3" t="n">
         <v>27</v>
       </c>
       <c r="AN3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AO3" t="n">
         <v>18</v>
@@ -972,28 +1039,28 @@
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW3" t="n">
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA3" t="n">
         <v>17</v>
       </c>
       <c r="BB3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC3" t="n">
         <v>15</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E4" t="n">
         <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>0.583</v>
+        <v>0.592</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1046,7 +1113,7 @@
         <v>79.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L4" t="n">
         <v>7.7</v>
@@ -1055,31 +1122,31 @@
         <v>21.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.356</v>
+        <v>0.358</v>
       </c>
       <c r="O4" t="n">
         <v>17.4</v>
       </c>
       <c r="P4" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.732</v>
+        <v>0.737</v>
       </c>
       <c r="R4" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="S4" t="n">
         <v>30.1</v>
       </c>
       <c r="T4" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U4" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V4" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W4" t="n">
         <v>7.2</v>
@@ -1091,19 +1158,19 @@
         <v>4.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>96</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1133,22 +1200,22 @@
         <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AO4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR4" t="n">
         <v>6</v>
       </c>
       <c r="AS4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
@@ -1157,25 +1224,25 @@
         <v>28</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
         <v>23</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
         <v>12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -1207,43 +1274,43 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E5" t="n">
         <v>17</v>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
-        <v>0.236</v>
+        <v>0.239</v>
       </c>
       <c r="H5" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I5" t="n">
         <v>34.3</v>
       </c>
       <c r="J5" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.421</v>
+        <v>0.42</v>
       </c>
       <c r="L5" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M5" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="N5" t="n">
-        <v>0.337</v>
+        <v>0.336</v>
       </c>
       <c r="O5" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="P5" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q5" t="n">
         <v>0.747</v>
@@ -1252,10 +1319,10 @@
         <v>11.3</v>
       </c>
       <c r="S5" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="T5" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="U5" t="n">
         <v>19.1</v>
@@ -1270,34 +1337,34 @@
         <v>6</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC5" t="n">
         <v>-9.699999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
       </c>
       <c r="AF5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG5" t="n">
         <v>30</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
         <v>30</v>
@@ -1342,7 +1409,7 @@
         <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
@@ -1497,10 +1564,10 @@
         <v>29</v>
       </c>
       <c r="AN6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP6" t="n">
         <v>22</v>
@@ -1524,7 +1591,7 @@
         <v>12</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX6" t="n">
         <v>11</v>
@@ -1539,10 +1606,10 @@
         <v>18</v>
       </c>
       <c r="BB6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E7" t="n">
         <v>22</v>
       </c>
       <c r="F7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>0.31</v>
+        <v>0.314</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
@@ -1595,22 +1662,22 @@
         <v>0.434</v>
       </c>
       <c r="L7" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="O7" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P7" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="R7" t="n">
         <v>12.3</v>
@@ -1619,7 +1686,7 @@
         <v>28.3</v>
       </c>
       <c r="T7" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="U7" t="n">
         <v>20.6</v>
@@ -1637,19 +1704,19 @@
         <v>7.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.3</v>
+        <v>-4.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
@@ -1685,13 +1752,13 @@
         <v>13</v>
       </c>
       <c r="AP7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS7" t="n">
         <v>30</v>
@@ -1703,7 +1770,7 @@
         <v>26</v>
       </c>
       <c r="AV7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
         <v>14</v>
@@ -1715,10 +1782,10 @@
         <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB7" t="n">
         <v>17</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
         <v>17</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
         <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>0.676</v>
+        <v>0.671</v>
       </c>
       <c r="H9" t="n">
         <v>48.5</v>
@@ -1953,10 +2020,10 @@
         <v>40.5</v>
       </c>
       <c r="J9" t="n">
-        <v>84.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L9" t="n">
         <v>6.3</v>
@@ -1965,34 +2032,34 @@
         <v>18.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.34</v>
+        <v>0.341</v>
       </c>
       <c r="O9" t="n">
         <v>18.2</v>
       </c>
       <c r="P9" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.699</v>
+        <v>0.7</v>
       </c>
       <c r="R9" t="n">
         <v>13.3</v>
       </c>
       <c r="S9" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T9" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="U9" t="n">
         <v>24.2</v>
       </c>
       <c r="V9" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X9" t="n">
         <v>6.5</v>
@@ -2001,7 +2068,7 @@
         <v>6.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA9" t="n">
         <v>21.8</v>
@@ -2010,7 +2077,7 @@
         <v>105.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD9" t="n">
         <v>1</v>
@@ -2019,10 +2086,10 @@
         <v>4</v>
       </c>
       <c r="AF9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH9" t="n">
         <v>7</v>
@@ -2034,7 +2101,7 @@
         <v>2</v>
       </c>
       <c r="AK9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL9" t="n">
         <v>21</v>
@@ -2061,7 +2128,7 @@
         <v>12</v>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="n">
         <v>3</v>
@@ -2079,7 +2146,7 @@
         <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
         <v>3</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E10" t="n">
         <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G10" t="n">
-        <v>0.329</v>
+        <v>0.333</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2138,7 +2205,7 @@
         <v>81.2</v>
       </c>
       <c r="K10" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L10" t="n">
         <v>6.2</v>
@@ -2147,7 +2214,7 @@
         <v>17.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O10" t="n">
         <v>15.7</v>
@@ -2156,25 +2223,25 @@
         <v>22.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.697</v>
+        <v>0.698</v>
       </c>
       <c r="R10" t="n">
         <v>12.2</v>
       </c>
       <c r="S10" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T10" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U10" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V10" t="n">
         <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X10" t="n">
         <v>5.1</v>
@@ -2183,19 +2250,19 @@
         <v>5.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>93.8</v>
+        <v>94</v>
       </c>
       <c r="AC10" t="n">
-        <v>-5.1</v>
+        <v>-4.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE10" t="n">
         <v>26</v>
@@ -2216,7 +2283,7 @@
         <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL10" t="n">
         <v>23</v>
@@ -2225,7 +2292,7 @@
         <v>24</v>
       </c>
       <c r="AN10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
         <v>23</v>
@@ -2249,7 +2316,7 @@
         <v>23</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW10" t="n">
         <v>26</v>
@@ -2264,7 +2331,7 @@
         <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB10" t="n">
         <v>25</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>0.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>10</v>
@@ -2389,10 +2456,10 @@
         <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ11" t="n">
         <v>9</v>
@@ -2416,7 +2483,7 @@
         <v>18</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR11" t="n">
         <v>23</v>
@@ -2425,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="AT11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
         <v>14</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E12" t="n">
         <v>39</v>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>0.542</v>
+        <v>0.549</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
@@ -2523,16 +2590,16 @@
         <v>0.756</v>
       </c>
       <c r="R12" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S12" t="n">
-        <v>32</v>
+        <v>32.2</v>
       </c>
       <c r="T12" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U12" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V12" t="n">
         <v>16.4</v>
@@ -2544,28 +2611,28 @@
         <v>4</v>
       </c>
       <c r="Y12" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA12" t="n">
         <v>20.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>106</v>
+        <v>106.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
         <v>12</v>
       </c>
       <c r="AF12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG12" t="n">
         <v>13</v>
@@ -2580,13 +2647,13 @@
         <v>10</v>
       </c>
       <c r="AK12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL12" t="n">
         <v>2</v>
       </c>
       <c r="AM12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN12" t="n">
         <v>8</v>
@@ -2598,10 +2665,10 @@
         <v>5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS12" t="n">
         <v>8</v>
@@ -2625,7 +2692,7 @@
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
         <v>11</v>
@@ -2634,7 +2701,7 @@
         <v>2</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>5.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2750,10 +2817,10 @@
         <v>8</v>
       </c>
       <c r="AG13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
@@ -2795,7 +2862,7 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW13" t="n">
         <v>25</v>
@@ -2807,7 +2874,7 @@
         <v>21</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA13" t="n">
         <v>4</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E14" t="n">
         <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G14" t="n">
-        <v>0.671</v>
+        <v>0.681</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2866,34 +2933,34 @@
         <v>80.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L14" t="n">
         <v>7.6</v>
       </c>
       <c r="M14" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="O14" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P14" t="n">
         <v>23.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.707</v>
+        <v>0.708</v>
       </c>
       <c r="R14" t="n">
         <v>11.4</v>
       </c>
       <c r="S14" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T14" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U14" t="n">
         <v>23.5</v>
@@ -2920,19 +2987,19 @@
         <v>100.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
         <v>4</v>
       </c>
       <c r="AG14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH14" t="n">
         <v>28</v>
@@ -2944,7 +3011,7 @@
         <v>25</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>10</v>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
         <v>17</v>
@@ -2968,7 +3035,7 @@
         <v>15</v>
       </c>
       <c r="AS14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT14" t="n">
         <v>19</v>
@@ -2977,7 +3044,7 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -3105,10 +3172,10 @@
         <v>0.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF15" t="n">
         <v>15</v>
@@ -3117,7 +3184,7 @@
         <v>15</v>
       </c>
       <c r="AH15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI15" t="n">
         <v>14</v>
@@ -3153,7 +3220,7 @@
         <v>3</v>
       </c>
       <c r="AT15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU15" t="n">
         <v>17</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F16" t="n">
         <v>24</v>
       </c>
       <c r="G16" t="n">
-        <v>0.667</v>
+        <v>0.662</v>
       </c>
       <c r="H16" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J16" t="n">
         <v>81.8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L16" t="n">
         <v>4.7</v>
@@ -3248,7 +3315,7 @@
         <v>21.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.78</v>
+        <v>0.778</v>
       </c>
       <c r="R16" t="n">
         <v>13.2</v>
@@ -3278,37 +3345,37 @@
         <v>20.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
         <v>6</v>
       </c>
       <c r="AF16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG16" t="n">
         <v>6</v>
       </c>
       <c r="AH16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK16" t="n">
         <v>21</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>20</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3320,7 +3387,7 @@
         <v>23</v>
       </c>
       <c r="AO16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP16" t="n">
         <v>21</v>
@@ -3335,16 +3402,16 @@
         <v>26</v>
       </c>
       <c r="AT16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU16" t="n">
         <v>24</v>
       </c>
       <c r="AV16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX16" t="n">
         <v>14</v>
@@ -3356,7 +3423,7 @@
         <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB16" t="n">
         <v>26</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -3391,58 +3458,58 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E17" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F17" t="n">
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>0.792</v>
+        <v>0.789</v>
       </c>
       <c r="H17" t="n">
         <v>48.6</v>
       </c>
       <c r="I17" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="J17" t="n">
-        <v>78</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.497</v>
+        <v>0.496</v>
       </c>
       <c r="L17" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.393</v>
+        <v>0.391</v>
       </c>
       <c r="O17" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P17" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T17" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="U17" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V17" t="n">
         <v>13.5</v>
@@ -3451,7 +3518,7 @@
         <v>8.9</v>
       </c>
       <c r="X17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y17" t="n">
         <v>3.3</v>
@@ -3463,13 +3530,13 @@
         <v>20.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>103.5</v>
+        <v>103.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3493,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AM17" t="n">
         <v>9</v>
@@ -3508,13 +3575,13 @@
         <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3538,7 +3605,7 @@
         <v>8</v>
       </c>
       <c r="BA17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AE18" t="n">
         <v>17</v>
@@ -3702,10 +3769,10 @@
         <v>5</v>
       </c>
       <c r="AU18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW18" t="n">
         <v>11</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" t="n">
         <v>45</v>
       </c>
       <c r="G19" t="n">
-        <v>0.366</v>
+        <v>0.357</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
@@ -3782,19 +3849,19 @@
         <v>5.4</v>
       </c>
       <c r="M19" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3</v>
+        <v>0.299</v>
       </c>
       <c r="O19" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P19" t="n">
         <v>24.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.733</v>
+        <v>0.732</v>
       </c>
       <c r="R19" t="n">
         <v>12.3</v>
@@ -3812,37 +3879,37 @@
         <v>15</v>
       </c>
       <c r="W19" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X19" t="n">
         <v>4.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z19" t="n">
         <v>18.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.5</v>
+        <v>-2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF19" t="n">
         <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH19" t="n">
         <v>26</v>
@@ -3851,7 +3918,7 @@
         <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3872,31 +3939,31 @@
         <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS19" t="n">
         <v>17</v>
       </c>
       <c r="AT19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU19" t="n">
         <v>16</v>
       </c>
       <c r="AV19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW19" t="n">
         <v>12</v>
       </c>
       <c r="AX19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ19" t="n">
         <v>7</v>
@@ -3908,7 +3975,7 @@
         <v>20</v>
       </c>
       <c r="BC19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -3937,22 +4004,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E20" t="n">
         <v>25</v>
       </c>
       <c r="F20" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G20" t="n">
-        <v>0.342</v>
+        <v>0.347</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J20" t="n">
         <v>80.3</v>
@@ -3967,28 +4034,28 @@
         <v>18.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.366</v>
+        <v>0.367</v>
       </c>
       <c r="O20" t="n">
         <v>14.9</v>
       </c>
       <c r="P20" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R20" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S20" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T20" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U20" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V20" t="n">
         <v>14.4</v>
@@ -3997,7 +4064,7 @@
         <v>6.4</v>
       </c>
       <c r="X20" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y20" t="n">
         <v>6</v>
@@ -4009,16 +4076,16 @@
         <v>18.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>94</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.6</v>
+        <v>-3.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF20" t="n">
         <v>25</v>
@@ -4030,7 +4097,7 @@
         <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ20" t="n">
         <v>26</v>
@@ -4051,10 +4118,10 @@
         <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
         <v>12</v>
@@ -4063,13 +4130,13 @@
         <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU20" t="n">
         <v>22</v>
       </c>
       <c r="AV20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW20" t="n">
         <v>29</v>
@@ -4090,7 +4157,7 @@
         <v>24</v>
       </c>
       <c r="BC20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E21" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F21" t="n">
         <v>26</v>
       </c>
       <c r="G21" t="n">
-        <v>0.634</v>
+        <v>0.629</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
@@ -4137,43 +4204,43 @@
         <v>36.1</v>
       </c>
       <c r="J21" t="n">
-        <v>81.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L21" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="M21" t="n">
-        <v>28.7</v>
+        <v>28.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.37</v>
+        <v>0.369</v>
       </c>
       <c r="O21" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P21" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.76</v>
+        <v>0.758</v>
       </c>
       <c r="R21" t="n">
         <v>11</v>
       </c>
       <c r="S21" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T21" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="U21" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="V21" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="W21" t="n">
         <v>8.4</v>
@@ -4185,19 +4252,19 @@
         <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>99.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC21" t="n">
         <v>3.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE21" t="n">
         <v>8</v>
@@ -4206,7 +4273,7 @@
         <v>7</v>
       </c>
       <c r="AG21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH21" t="n">
         <v>30</v>
@@ -4218,25 +4285,25 @@
         <v>19</v>
       </c>
       <c r="AK21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
       </c>
       <c r="AM21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN21" t="n">
         <v>7</v>
       </c>
       <c r="AO21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AP21" t="n">
         <v>16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR21" t="n">
         <v>18</v>
@@ -4272,7 +4339,7 @@
         <v>11</v>
       </c>
       <c r="BC21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E22" t="n">
         <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G22" t="n">
-        <v>0.726</v>
+        <v>0.736</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4328,16 +4395,16 @@
         <v>7.3</v>
       </c>
       <c r="M22" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="O22" t="n">
         <v>22.8</v>
       </c>
       <c r="P22" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="Q22" t="n">
         <v>0.828</v>
@@ -4352,34 +4419,34 @@
         <v>43.4</v>
       </c>
       <c r="U22" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V22" t="n">
         <v>15.6</v>
       </c>
       <c r="W22" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X22" t="n">
         <v>7.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>106</v>
+        <v>106.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4430,13 +4497,13 @@
         <v>7</v>
       </c>
       <c r="AU22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV22" t="n">
         <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4448,7 +4515,7 @@
         <v>18</v>
       </c>
       <c r="BA22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F23" t="n">
         <v>54</v>
       </c>
       <c r="G23" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4510,16 +4577,16 @@
         <v>6.4</v>
       </c>
       <c r="M23" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.331</v>
+        <v>0.33</v>
       </c>
       <c r="O23" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="P23" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="Q23" t="n">
         <v>0.766</v>
@@ -4537,7 +4604,7 @@
         <v>23.1</v>
       </c>
       <c r="V23" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W23" t="n">
         <v>6.3</v>
@@ -4558,10 +4625,10 @@
         <v>94.40000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.6</v>
+        <v>-6.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4582,7 +4649,7 @@
         <v>7</v>
       </c>
       <c r="AK23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AL23" t="n">
         <v>20</v>
@@ -4600,7 +4667,7 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
         <v>24</v>
@@ -4615,7 +4682,7 @@
         <v>7</v>
       </c>
       <c r="AV23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F24" t="n">
         <v>43</v>
       </c>
       <c r="G24" t="n">
-        <v>0.403</v>
+        <v>0.394</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J24" t="n">
         <v>84</v>
       </c>
       <c r="K24" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L24" t="n">
         <v>6.3</v>
@@ -4695,16 +4762,16 @@
         <v>17.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.361</v>
+        <v>0.36</v>
       </c>
       <c r="O24" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.72</v>
+        <v>0.721</v>
       </c>
       <c r="R24" t="n">
         <v>10.9</v>
@@ -4713,13 +4780,13 @@
         <v>30.5</v>
       </c>
       <c r="T24" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U24" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V24" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W24" t="n">
         <v>7.3</v>
@@ -4731,7 +4798,7 @@
         <v>4.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA24" t="n">
         <v>16.2</v>
@@ -4740,10 +4807,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.5</v>
+        <v>-3.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4785,13 +4852,13 @@
         <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS24" t="n">
         <v>16</v>
       </c>
       <c r="AT24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU24" t="n">
         <v>10</v>
@@ -4803,22 +4870,22 @@
         <v>19</v>
       </c>
       <c r="AX24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY24" t="n">
         <v>13</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA24" t="n">
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BC24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-6.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>27</v>
@@ -4937,7 +5004,7 @@
         <v>27</v>
       </c>
       <c r="AH25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI25" t="n">
         <v>15</v>
@@ -4982,7 +5049,7 @@
         <v>28</v>
       </c>
       <c r="AW25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
@@ -4991,7 +5058,7 @@
         <v>17</v>
       </c>
       <c r="AZ25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E26" t="n">
         <v>33</v>
       </c>
       <c r="F26" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G26" t="n">
-        <v>0.458</v>
+        <v>0.465</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J26" t="n">
-        <v>82</v>
+        <v>82.2</v>
       </c>
       <c r="K26" t="n">
         <v>0.449</v>
       </c>
       <c r="L26" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M26" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="N26" t="n">
         <v>0.357</v>
       </c>
       <c r="O26" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="P26" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.776</v>
+        <v>0.777</v>
       </c>
       <c r="R26" t="n">
         <v>11</v>
@@ -5077,7 +5144,7 @@
         <v>30.5</v>
       </c>
       <c r="T26" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U26" t="n">
         <v>21.7</v>
@@ -5089,7 +5156,7 @@
         <v>6.7</v>
       </c>
       <c r="X26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y26" t="n">
         <v>4.2</v>
@@ -5104,10 +5171,10 @@
         <v>98.09999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5125,16 +5192,16 @@
         <v>17</v>
       </c>
       <c r="AJ26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AK26" t="n">
         <v>15</v>
       </c>
       <c r="AL26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN26" t="n">
         <v>16</v>
@@ -5146,10 +5213,10 @@
         <v>25</v>
       </c>
       <c r="AQ26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AS26" t="n">
         <v>15</v>
@@ -5161,13 +5228,13 @@
         <v>19</v>
       </c>
       <c r="AV26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW26" t="n">
         <v>28</v>
       </c>
       <c r="AX26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY26" t="n">
         <v>6</v>
@@ -5176,7 +5243,7 @@
         <v>5</v>
       </c>
       <c r="BA26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB26" t="n">
         <v>14</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -5289,19 +5356,19 @@
         <v>-4.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
         <v>21</v>
       </c>
       <c r="AF27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI27" t="n">
         <v>12</v>
@@ -5325,7 +5392,7 @@
         <v>9</v>
       </c>
       <c r="AP27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ27" t="n">
         <v>11</v>
@@ -5343,7 +5410,7 @@
         <v>25</v>
       </c>
       <c r="AV27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW27" t="n">
         <v>13</v>
@@ -5358,7 +5425,7 @@
         <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E28" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F28" t="n">
         <v>17</v>
       </c>
       <c r="G28" t="n">
-        <v>0.764</v>
+        <v>0.761</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
@@ -5411,19 +5478,19 @@
         <v>39.5</v>
       </c>
       <c r="J28" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.487</v>
+        <v>0.486</v>
       </c>
       <c r="L28" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.384</v>
+        <v>0.383</v>
       </c>
       <c r="O28" t="n">
         <v>17</v>
@@ -5432,25 +5499,25 @@
         <v>21.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.793</v>
+        <v>0.79</v>
       </c>
       <c r="R28" t="n">
         <v>8</v>
       </c>
       <c r="S28" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="T28" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U28" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="V28" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W28" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X28" t="n">
         <v>5.4</v>
@@ -5459,7 +5526,7 @@
         <v>4.7</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="AA28" t="n">
         <v>19.4</v>
@@ -5468,10 +5535,10 @@
         <v>104.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5495,7 +5562,7 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM28" t="n">
         <v>6</v>
@@ -5510,7 +5577,7 @@
         <v>17</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5525,7 +5592,7 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -5575,43 +5642,43 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F29" t="n">
         <v>45</v>
       </c>
       <c r="G29" t="n">
-        <v>0.375</v>
+        <v>0.366</v>
       </c>
       <c r="H29" t="n">
         <v>48.8</v>
       </c>
       <c r="I29" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J29" t="n">
         <v>82</v>
       </c>
       <c r="K29" t="n">
-        <v>0.444</v>
+        <v>0.442</v>
       </c>
       <c r="L29" t="n">
         <v>7.1</v>
       </c>
       <c r="M29" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="N29" t="n">
         <v>0.34</v>
       </c>
       <c r="O29" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="P29" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="Q29" t="n">
         <v>0.786</v>
@@ -5620,10 +5687,10 @@
         <v>10.9</v>
       </c>
       <c r="S29" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T29" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="U29" t="n">
         <v>21.5</v>
@@ -5635,34 +5702,34 @@
         <v>7.4</v>
       </c>
       <c r="X29" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y29" t="n">
         <v>4.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB29" t="n">
         <v>97.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.1</v>
+        <v>-2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF29" t="n">
         <v>21</v>
       </c>
       <c r="AG29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH29" t="n">
         <v>2</v>
@@ -5674,7 +5741,7 @@
         <v>12</v>
       </c>
       <c r="AK29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL29" t="n">
         <v>14</v>
@@ -5683,10 +5750,10 @@
         <v>10</v>
       </c>
       <c r="AN29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
@@ -5695,7 +5762,7 @@
         <v>5</v>
       </c>
       <c r="AR29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
@@ -5704,7 +5771,7 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV29" t="n">
         <v>4</v>
@@ -5713,7 +5780,7 @@
         <v>18</v>
       </c>
       <c r="AX29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY29" t="n">
         <v>14</v>
@@ -5722,7 +5789,7 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB29" t="n">
         <v>16</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -5757,25 +5824,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E30" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F30" t="n">
         <v>36</v>
       </c>
       <c r="G30" t="n">
-        <v>0.507</v>
+        <v>0.5</v>
       </c>
       <c r="H30" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I30" t="n">
         <v>37</v>
       </c>
       <c r="J30" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="K30" t="n">
         <v>0.451</v>
@@ -5784,16 +5851,16 @@
         <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.361</v>
+        <v>0.363</v>
       </c>
       <c r="O30" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P30" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q30" t="n">
         <v>0.766</v>
@@ -5811,10 +5878,10 @@
         <v>22.5</v>
       </c>
       <c r="V30" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W30" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X30" t="n">
         <v>6.4</v>
@@ -5823,28 +5890,28 @@
         <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AA30" t="n">
         <v>20.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF30" t="n">
         <v>15</v>
       </c>
       <c r="AG30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH30" t="n">
         <v>6</v>
@@ -5853,13 +5920,13 @@
         <v>16</v>
       </c>
       <c r="AJ30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AK30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM30" t="n">
         <v>28</v>
@@ -5871,16 +5938,16 @@
         <v>7</v>
       </c>
       <c r="AP30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
         <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT30" t="n">
         <v>13</v>
@@ -5889,22 +5956,22 @@
         <v>13</v>
       </c>
       <c r="AV30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX30" t="n">
         <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ30" t="n">
         <v>29</v>
       </c>
       <c r="BA30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB30" t="n">
         <v>13</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
@@ -5939,22 +6006,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E31" t="n">
         <v>26</v>
       </c>
       <c r="F31" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G31" t="n">
-        <v>0.361</v>
+        <v>0.366</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="J31" t="n">
         <v>81.59999999999999</v>
@@ -5969,37 +6036,37 @@
         <v>18.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.362</v>
+        <v>0.365</v>
       </c>
       <c r="O31" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="P31" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.738</v>
+        <v>0.735</v>
       </c>
       <c r="R31" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S31" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T31" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="U31" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V31" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W31" t="n">
         <v>7.3</v>
       </c>
       <c r="X31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y31" t="n">
         <v>4.5</v>
@@ -6017,16 +6084,16 @@
         <v>-2.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AH31" t="n">
         <v>8</v>
@@ -6056,10 +6123,10 @@
         <v>24</v>
       </c>
       <c r="AQ31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS31" t="n">
         <v>7</v>
@@ -6074,10 +6141,10 @@
         <v>27</v>
       </c>
       <c r="AW31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY31" t="n">
         <v>9</v>
@@ -6092,7 +6159,7 @@
         <v>28</v>
       </c>
       <c r="BC31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-29-2012-13</t>
+          <t>2013-03-29</t>
         </is>
       </c>
     </row>
